--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/WASHINGTON_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/WASHINGTON_2021.xlsx
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C103">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C176">
@@ -8041,7 +8041,7 @@
         <v>47</v>
       </c>
       <c r="D427">
-        <v>0.009310618066561015</v>
+        <v>0.009310618066561017</v>
       </c>
     </row>
     <row r="428">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>San Bartolome Yucane</t>
+          <t>San Bartolome Yucuane</t>
         </is>
       </c>
       <c r="C568">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C594">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C595">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C629">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C630">
